--- a/results/metrics.xlsx
+++ b/results/metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Mi unidad\Deep Learning\gene_knockout\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABC1D10-735D-4D54-9BCA-441395139E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAFE9A2-BE2C-46B3-997B-91B21B3EE5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Splitting mode (baseline)" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Dim reduct (original MLP)" sheetId="3" r:id="rId3"/>
     <sheet name="Loss function (original MLP)" sheetId="4" r:id="rId4"/>
     <sheet name="Modifications (SkipCon MLP)" sheetId="5" r:id="rId5"/>
+    <sheet name="Crossed cell lines" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="18">
   <si>
     <t>MSE</t>
   </si>
@@ -74,9 +75,6 @@
     </r>
   </si>
   <si>
-    <t>Learning rate</t>
-  </si>
-  <si>
     <t>Top n genes</t>
   </si>
   <si>
@@ -95,13 +93,22 @@
     <t>Batch Normalization</t>
   </si>
   <si>
-    <t>Skip connection</t>
-  </si>
-  <si>
-    <t>BN + SC</t>
-  </si>
-  <si>
-    <t>Crossed-cell lines</t>
+    <t>Batch Normalization and Skip Connection</t>
+  </si>
+  <si>
+    <t>LR</t>
+  </si>
+  <si>
+    <t>Skip Connection</t>
+  </si>
+  <si>
+    <t>Training cell line</t>
+  </si>
+  <si>
+    <t>PC3</t>
+  </si>
+  <si>
+    <t>A549</t>
   </si>
 </sst>
 </file>
@@ -147,7 +154,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -164,11 +171,66 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9"/>
+      </right>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -185,6 +247,34 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,42 +555,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="9">
         <v>6.5449999999999994E-2</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="9">
         <v>0.79879</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="10">
         <v>9.5640000000000003E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -514,8 +604,12 @@
         <v>0.34399999999999997</v>
       </c>
     </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G10" s="7"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -524,13 +618,13 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -544,8 +638,8 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
-        <f>0.001</f>
-        <v>1E-3</v>
+        <f>0.0001</f>
+        <v>1E-4</v>
       </c>
       <c r="B2" s="4">
         <v>6.5009999999999998E-2</v>
@@ -558,17 +652,17 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
-        <f>0.0001</f>
-        <v>1E-4</v>
-      </c>
-      <c r="B3" s="4">
+      <c r="A3" s="11">
+        <f>0.00001</f>
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="B3" s="12">
         <v>6.7549999999999999E-2</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="12">
         <v>0.80034000000000005</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="13">
         <v>8.2530000000000006E-2</v>
       </c>
     </row>
@@ -594,16 +688,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF3FD14B-040C-426A-BC52-99111802340F}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -615,7 +709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>1000</v>
       </c>
@@ -629,7 +723,7 @@
         <v>8.2530000000000006E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>2000</v>
       </c>
@@ -643,21 +737,21 @@
         <v>8.1559999999999994E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="15">
         <v>3000</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="9">
         <v>3.6769999999999997E-2</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="9">
         <v>0.84540000000000004</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="10">
         <v>9.4200000000000006E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>4000</v>
       </c>
@@ -671,7 +765,7 @@
         <v>7.8369999999999995E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>5000</v>
       </c>
@@ -684,8 +778,9 @@
       <c r="D6" s="1">
         <v>7.4310000000000001E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -707,7 +802,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -721,7 +816,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1">
         <v>3.6769999999999997E-2</v>
@@ -735,7 +830,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1">
         <v>4.1680000000000002E-2</v>
@@ -757,13 +852,13 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -777,7 +872,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1">
         <v>5.9110000000000003E-2</v>
@@ -791,7 +886,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1">
         <v>5.3449999999999998E-2</v>
@@ -804,35 +899,96 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1">
+      <c r="A4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="9">
         <v>5.3769999999999998E-2</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="9">
         <v>0.77449000000000001</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="10">
         <v>0.68911999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0.11743000000000001</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0.63253000000000004</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0.53222000000000003</v>
-      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF8EB83-414B-4A02-BD14-53E6DE23239A}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="35.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="9">
+        <v>8.4510000000000002E-2</v>
+      </c>
+      <c r="C2" s="9">
+        <v>0.69340999999999997</v>
+      </c>
+      <c r="D2" s="10">
+        <v>0.74353000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.12137000000000001</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.60067999999999999</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.52956999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="16"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E8" s="17"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>